--- a/outputs/2026-02-04/email_reports/Servicestyckarna.xlsx
+++ b/outputs/2026-02-04/email_reports/Servicestyckarna.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-10</t>
         </is>
       </c>
     </row>
